--- a/data/trans_orig/P17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2007</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2007 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126543</t>
+          <t>129407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170621</t>
+          <t>170960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>47336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76207</t>
+          <t>76219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183710</t>
+          <t>183362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236664</t>
+          <t>235620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90211</t>
+          <t>92137</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128876</t>
+          <t>129967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163484</t>
+          <t>163033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207528</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>266799</t>
+          <t>263368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>325416</t>
+          <t>324420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>56709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89805</t>
+          <t>90119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82741</t>
+          <t>82406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115895</t>
+          <t>113661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160045</t>
+          <t>160418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>333240</t>
+          <t>329164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387434</t>
+          <t>384538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347240</t>
+          <t>349751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401959</t>
+          <t>401477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698003</t>
+          <t>699556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769266</t>
+          <t>775523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>27167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51119</t>
+          <t>52883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208938</t>
+          <t>208579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263392</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>96698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138399</t>
+          <t>139206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316386</t>
+          <t>318102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>386041</t>
+          <t>389810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114896</t>
+          <t>114721</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156599</t>
+          <t>159233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>198050</t>
+          <t>199527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>249659</t>
+          <t>252598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>328904</t>
+          <t>329267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>396565</t>
+          <t>400696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>57417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94209</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62838</t>
+          <t>63424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98455</t>
+          <t>100791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131449</t>
+          <t>128933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182231</t>
+          <t>180107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461961</t>
+          <t>460918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526268</t>
+          <t>524812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502427</t>
+          <t>502111</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>566869</t>
+          <t>564686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>980028</t>
+          <t>975538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1071723</t>
+          <t>1066776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>36515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163286</t>
+          <t>165967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211473</t>
+          <t>213294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80554</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113780</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255193</t>
+          <t>256442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315931</t>
+          <t>317089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73429</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111610</t>
+          <t>110231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133346</t>
+          <t>132770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>173744</t>
+          <t>177068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215761</t>
+          <t>215778</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>271707</t>
+          <t>272217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>77507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>112205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>61487</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>94186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147994</t>
+          <t>147274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196486</t>
+          <t>195316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261198</t>
+          <t>261377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312586</t>
+          <t>313904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>327422</t>
+          <t>326065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>377434</t>
+          <t>374729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599638</t>
+          <t>602397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>675570</t>
+          <t>680035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>36042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>58900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208544</t>
+          <t>207031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>260327</t>
+          <t>260050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121963</t>
+          <t>122282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167289</t>
+          <t>165759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>344245</t>
+          <t>341859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>411600</t>
+          <t>413045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>55414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87113</t>
+          <t>86619</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128974</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171058</t>
+          <t>173184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>192830</t>
+          <t>191420</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>246259</t>
+          <t>248409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>99793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140095</t>
+          <t>139673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91098</t>
+          <t>90612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130327</t>
+          <t>130674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>199879</t>
+          <t>200489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>255214</t>
+          <t>256056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>467420</t>
+          <t>465445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>527141</t>
+          <t>528773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>577677</t>
+          <t>578050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641164</t>
+          <t>643035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1068320</t>
+          <t>1059851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1151260</t>
+          <t>1150725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49569</t>
+          <t>48302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83393</t>
+          <t>83009</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61899</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>135443</t>
+          <t>135092</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>753882</t>
+          <t>753059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>858773</t>
+          <t>859011</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>376180</t>
+          <t>380387</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>452717</t>
+          <t>456228</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1159164</t>
+          <t>1157819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1285271</t>
+          <t>1286787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>367503</t>
+          <t>372666</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>446232</t>
+          <t>451588</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>665119</t>
+          <t>663545</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>756429</t>
+          <t>756134</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1056489</t>
+          <t>1061833</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1178340</t>
+          <t>1176269</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>322044</t>
+          <t>319761</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>395820</t>
+          <t>395821</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>297060</t>
+          <t>296473</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>366111</t>
+          <t>364573</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>643821</t>
+          <t>641301</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>738551</t>
+          <t>743801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1578044</t>
+          <t>1573694</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1692511</t>
+          <t>1691361</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1817794</t>
+          <t>1816905</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1934341</t>
+          <t>1929458</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3427518</t>
+          <t>3429401</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3587028</t>
+          <t>3582992</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2012</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95753</t>
+          <t>93908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134402</t>
+          <t>133881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63037</t>
+          <t>64045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140201</t>
+          <t>138195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187604</t>
+          <t>188452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102510</t>
+          <t>102655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141539</t>
+          <t>142941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149191</t>
+          <t>147526</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194161</t>
+          <t>192325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261009</t>
+          <t>262878</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>324855</t>
+          <t>326100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71285</t>
+          <t>72371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75141</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97026</t>
+          <t>94639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138923</t>
+          <t>136584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379085</t>
+          <t>380221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431547</t>
+          <t>432308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>389841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441513</t>
+          <t>440713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>785633</t>
+          <t>784115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>861735</t>
+          <t>859548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127097</t>
+          <t>125797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173934</t>
+          <t>173463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>59593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95642</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197202</t>
+          <t>197379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259957</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126149</t>
+          <t>127664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173127</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>219819</t>
+          <t>220114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275664</t>
+          <t>275437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>357884</t>
+          <t>359255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430404</t>
+          <t>434152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87034</t>
+          <t>87547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127291</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>69965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109002</t>
+          <t>108508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168894</t>
+          <t>169082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220858</t>
+          <t>223857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559902</t>
+          <t>558641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628464</t>
+          <t>625576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581147</t>
+          <t>583840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648369</t>
+          <t>647368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1161849</t>
+          <t>1157756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1253780</t>
+          <t>1251570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,47 +5789,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>18798</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>10991</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>30269</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>18798</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>11394</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>30857</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>133220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179002</t>
+          <t>177863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56285</t>
+          <t>55923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90830</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198726</t>
+          <t>201074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258253</t>
+          <t>259583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>73087</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114829</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142350</t>
+          <t>144344</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187264</t>
+          <t>190720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>227989</t>
+          <t>229328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>289809</t>
+          <t>287338</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78522</t>
+          <t>77334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119120</t>
+          <t>119081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73359</t>
+          <t>72834</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112187</t>
+          <t>110915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160929</t>
+          <t>159729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>215258</t>
+          <t>216240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>376055</t>
+          <t>376019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>433257</t>
+          <t>436217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>407373</t>
+          <t>407635</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>466162</t>
+          <t>465819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796326</t>
+          <t>800542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883446</t>
+          <t>884515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32873</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49605</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152382</t>
+          <t>152804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200514</t>
+          <t>200794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59706</t>
+          <t>60382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95477</t>
+          <t>95696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224773</t>
+          <t>221370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282417</t>
+          <t>283719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136625</t>
+          <t>135299</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>185561</t>
+          <t>184205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236105</t>
+          <t>233835</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>292936</t>
+          <t>289019</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>386263</t>
+          <t>383225</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>460695</t>
+          <t>461317</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>107413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74198</t>
+          <t>73666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110262</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>154152</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203871</t>
+          <t>205217</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>476118</t>
+          <t>475026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>537833</t>
+          <t>538066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>575942</t>
+          <t>574271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641122</t>
+          <t>638117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1067718</t>
+          <t>1067642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1159709</t>
+          <t>1163129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>36668</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67562</t>
+          <t>68433</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>46645</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63609</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102181</t>
+          <t>104307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>548612</t>
+          <t>551820</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>642360</t>
+          <t>642291</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>240663</t>
+          <t>240871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>310579</t>
+          <t>302236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>814145</t>
+          <t>816962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>926768</t>
+          <t>930253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>477718</t>
+          <t>477526</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>567074</t>
+          <t>561977</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>795935</t>
+          <t>791840</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>897406</t>
+          <t>895371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1299063</t>
+          <t>1297649</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1444883</t>
+          <t>1443981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>309490</t>
+          <t>311467</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>383759</t>
+          <t>385516</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>291218</t>
+          <t>296776</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>362555</t>
+          <t>370602</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>621262</t>
+          <t>622930</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>726503</t>
+          <t>723286</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1846565</t>
+          <t>1850558</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1968126</t>
+          <t>1975531</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2015578</t>
+          <t>2018523</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2138111</t>
+          <t>2138063</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3908010</t>
+          <t>3905641</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4079530</t>
+          <t>4073875</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2016</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>87204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126604</t>
+          <t>126526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40700</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67205</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135448</t>
+          <t>136616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183335</t>
+          <t>186357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50511</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80327</t>
+          <t>83028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67825</t>
+          <t>67313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102267</t>
+          <t>100903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>125364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172284</t>
+          <t>171665</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33587</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26962</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51067</t>
+          <t>51206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77492</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442011</t>
+          <t>439493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489179</t>
+          <t>488100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455207</t>
+          <t>456761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501910</t>
+          <t>501613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>910964</t>
+          <t>911802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977883</t>
+          <t>977751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>25972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141322</t>
+          <t>138318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>189374</t>
+          <t>188459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>59545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93102</t>
+          <t>91380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209341</t>
+          <t>209770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>271559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85521</t>
+          <t>84842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125620</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141623</t>
+          <t>142807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192795</t>
+          <t>190109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240761</t>
+          <t>239928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>302514</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50541</t>
+          <t>49998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83190</t>
+          <t>82058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>61673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98727</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>118357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167857</t>
+          <t>165983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641404</t>
+          <t>642366</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>705492</t>
+          <t>704586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680009</t>
+          <t>681233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746739</t>
+          <t>741712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1342011</t>
+          <t>1338669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1427623</t>
+          <t>1435007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122385</t>
+          <t>121391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166074</t>
+          <t>168574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62881</t>
+          <t>63447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97614</t>
+          <t>99159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195016</t>
+          <t>192551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249250</t>
+          <t>250939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94429</t>
+          <t>94386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135905</t>
+          <t>135592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>109137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>153661</t>
+          <t>151361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215730</t>
+          <t>215398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>273007</t>
+          <t>272946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61328</t>
+          <t>59585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95945</t>
+          <t>94204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>67475</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103644</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137223</t>
+          <t>135788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184628</t>
+          <t>185032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>388866</t>
+          <t>390504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>446103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>457205</t>
+          <t>459182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>512682</t>
+          <t>515537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>865563</t>
+          <t>865334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942919</t>
+          <t>945223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,47 +10078,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10184</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18884</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10184</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>18207</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161359</t>
+          <t>160385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209578</t>
+          <t>209396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108312</t>
+          <t>107004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152015</t>
+          <t>148321</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276908</t>
+          <t>278868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>341528</t>
+          <t>345660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84127</t>
+          <t>83219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122070</t>
+          <t>122380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126387</t>
+          <t>127090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171516</t>
+          <t>174036</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>218957</t>
+          <t>219829</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>284516</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53555</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>85945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67401</t>
+          <t>68984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103385</t>
+          <t>103288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131053</t>
+          <t>132007</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>542687</t>
+          <t>541664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>601774</t>
+          <t>601962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>636353</t>
+          <t>634817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701454</t>
+          <t>699111</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1198623</t>
+          <t>1193588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1285470</t>
+          <t>1283535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,98%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60637</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51456</t>
+          <t>53548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>68007</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102939</t>
+          <t>104964</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>547137</t>
+          <t>551885</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>641519</t>
+          <t>642525</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>295573</t>
+          <t>301051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>368895</t>
+          <t>370292</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>871578</t>
+          <t>869861</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>992657</t>
+          <t>986752</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>348377</t>
+          <t>347590</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>424222</t>
+          <t>423832</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>487843</t>
+          <t>484213</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>568397</t>
+          <t>568485</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>855731</t>
+          <t>859747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>969756</t>
+          <t>969990</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>201800</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>262996</t>
+          <t>258821</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>254489</t>
+          <t>251288</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>317878</t>
+          <t>317523</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>473075</t>
+          <t>473122</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>558574</t>
+          <t>561843</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2072076</t>
+          <t>2073341</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2185328</t>
+          <t>2187139</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2288496</t>
+          <t>2294905</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2401851</t>
+          <t>2405724</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4390196</t>
+          <t>4393815</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4550755</t>
+          <t>4554412</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2023</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>136599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185802</t>
+          <t>188310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>97470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129825</t>
+          <t>129023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243950</t>
+          <t>245874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306279</t>
+          <t>307809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>58151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84370</t>
+          <t>86837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84942</t>
+          <t>85671</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127894</t>
+          <t>127112</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>40650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36945</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384660</t>
+          <t>385517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439796</t>
+          <t>439446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441923</t>
+          <t>441167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480670</t>
+          <t>480764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840768</t>
+          <t>837531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>910071</t>
+          <t>907847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104449</t>
+          <t>93703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269787</t>
+          <t>271129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131903</t>
+          <t>131611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171950</t>
+          <t>174562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233633</t>
+          <t>241836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>417002</t>
+          <t>417142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48713</t>
+          <t>41382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127087</t>
+          <t>126371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>116361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158975</t>
+          <t>156569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155377</t>
+          <t>155989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271633</t>
+          <t>271050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48190</t>
+          <t>50259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>699365</t>
+          <t>742369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45381</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>71357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105303</t>
+          <t>105549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>916583</t>
+          <t>909914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325667</t>
+          <t>289893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>757496</t>
+          <t>756855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581702</t>
+          <t>578448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633220</t>
+          <t>633382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>811121</t>
+          <t>816546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1365713</t>
+          <t>1368342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>37939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164003</t>
+          <t>166683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221170</t>
+          <t>224630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37257</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112008</t>
+          <t>112439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176183</t>
+          <t>180449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329466</t>
+          <t>326581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63288</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103111</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125720</t>
+          <t>126508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237479</t>
+          <t>238692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77322</t>
+          <t>76858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>113615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89745</t>
+          <t>95547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173120</t>
+          <t>176562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325014</t>
+          <t>322615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>386665</t>
+          <t>383200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>557288</t>
+          <t>555753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>798195</t>
+          <t>795718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>896137</t>
+          <t>899292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1231753</t>
+          <t>1219436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205370</t>
+          <t>201936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264621</t>
+          <t>263829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126364</t>
+          <t>127401</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186158</t>
+          <t>185050</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>345131</t>
+          <t>349445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>438060</t>
+          <t>442761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60031</t>
+          <t>59071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94841</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77348</t>
+          <t>79580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118729</t>
+          <t>119331</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>146484</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>197880</t>
+          <t>199627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>40656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72806</t>
+          <t>71647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55505</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103054</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147752</t>
+          <t>146679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>521859</t>
+          <t>523991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>587537</t>
+          <t>589255</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718174</t>
+          <t>718912</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819208</t>
+          <t>824461</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1256596</t>
+          <t>1259087</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1392306</t>
+          <t>1386615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54420</t>
+          <t>53581</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67322</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>598162</t>
+          <t>612285</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>879137</t>
+          <t>871588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>426641</t>
+          <t>417820</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>563988</t>
+          <t>560606</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1120246</t>
+          <t>1119069</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1406069</t>
+          <t>1402991</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>219380</t>
+          <t>221838</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>325250</t>
+          <t>324660</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>345438</t>
+          <t>348084</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>463315</t>
+          <t>465546</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>608568</t>
+          <t>612226</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>768921</t>
+          <t>767923</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>182904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1199400</t>
+          <t>1047063</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>200401</t>
+          <t>196410</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>273638</t>
+          <t>271580</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>418077</t>
+          <t>423660</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1553832</t>
+          <t>1442278</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1447196</t>
+          <t>1510435</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2075126</t>
+          <t>2080029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2374759</t>
+          <t>2371139</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2680023</t>
+          <t>2688514</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3881546</t>
+          <t>3856563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4622512</t>
+          <t>4610202</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129407</t>
+          <t>126254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170960</t>
+          <t>168831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76219</t>
+          <t>75818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183362</t>
+          <t>185392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235620</t>
+          <t>236185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92137</t>
+          <t>91270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129967</t>
+          <t>128177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163033</t>
+          <t>161974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206738</t>
+          <t>206689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>263368</t>
+          <t>262621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>324420</t>
+          <t>323684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56709</t>
+          <t>55433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90119</t>
+          <t>90250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52114</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>116155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160418</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329164</t>
+          <t>331082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>384538</t>
+          <t>384526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349751</t>
+          <t>351764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401477</t>
+          <t>402606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699556</t>
+          <t>695428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775523</t>
+          <t>772792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>35020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27167</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208579</t>
+          <t>207759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263416</t>
+          <t>262205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96698</t>
+          <t>95698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139206</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318102</t>
+          <t>315223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>389810</t>
+          <t>385833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114721</t>
+          <t>114856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159233</t>
+          <t>159891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199527</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252598</t>
+          <t>255222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329267</t>
+          <t>329114</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>400696</t>
+          <t>397550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57417</t>
+          <t>57452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>63573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100791</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128933</t>
+          <t>129259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180107</t>
+          <t>181897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460918</t>
+          <t>459505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524812</t>
+          <t>523541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502111</t>
+          <t>501486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>564686</t>
+          <t>562535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>975538</t>
+          <t>981015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1066776</t>
+          <t>1073833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27667</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>37274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165967</t>
+          <t>161427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213294</t>
+          <t>211378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79630</t>
+          <t>78295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>115005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256442</t>
+          <t>253712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>317089</t>
+          <t>316526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72752</t>
+          <t>73734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110231</t>
+          <t>109342</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>132770</t>
+          <t>133492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177068</t>
+          <t>175322</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215778</t>
+          <t>216618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>272217</t>
+          <t>275179</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77507</t>
+          <t>77181</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112205</t>
+          <t>113854</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61487</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94186</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147274</t>
+          <t>148602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195316</t>
+          <t>197250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261377</t>
+          <t>261267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313904</t>
+          <t>312678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326065</t>
+          <t>326589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374729</t>
+          <t>375539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602397</t>
+          <t>599910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>680035</t>
+          <t>676075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30320</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58900</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207031</t>
+          <t>208262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>260050</t>
+          <t>260565</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122282</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165759</t>
+          <t>168934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>341859</t>
+          <t>341402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413045</t>
+          <t>413214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55414</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86619</t>
+          <t>86284</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126556</t>
+          <t>125346</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173184</t>
+          <t>171814</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>191420</t>
+          <t>193723</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>248409</t>
+          <t>246039</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99793</t>
+          <t>97520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139673</t>
+          <t>138089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90612</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130674</t>
+          <t>129545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200489</t>
+          <t>201109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>256056</t>
+          <t>253831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>465445</t>
+          <t>467871</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>528773</t>
+          <t>524646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>578050</t>
+          <t>575267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>643035</t>
+          <t>640301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1059851</t>
+          <t>1059863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1150725</t>
+          <t>1149818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48302</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83009</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89176</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>135092</t>
+          <t>136733</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>753059</t>
+          <t>754491</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>859011</t>
+          <t>857717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>380387</t>
+          <t>378859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>456228</t>
+          <t>456917</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1157819</t>
+          <t>1154167</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1286787</t>
+          <t>1284010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>372666</t>
+          <t>369908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>451588</t>
+          <t>445717</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>663545</t>
+          <t>663542</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>756134</t>
+          <t>758175</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1061833</t>
+          <t>1060406</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1176269</t>
+          <t>1177739</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>319761</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>395821</t>
+          <t>397528</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>296473</t>
+          <t>295676</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>364573</t>
+          <t>369384</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>641301</t>
+          <t>638099</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>743801</t>
+          <t>741585</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1573694</t>
+          <t>1578259</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1691361</t>
+          <t>1698630</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1816905</t>
+          <t>1816964</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1929458</t>
+          <t>1931644</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3429401</t>
+          <t>3419936</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3582992</t>
+          <t>3587905</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93908</t>
+          <t>95829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133881</t>
+          <t>135027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36208</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64045</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138195</t>
+          <t>139795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188452</t>
+          <t>188989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102655</t>
+          <t>101643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>142373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147526</t>
+          <t>145413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>192325</t>
+          <t>194627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>262878</t>
+          <t>261919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326100</t>
+          <t>327418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72371</t>
+          <t>72120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46187</t>
+          <t>46121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76600</t>
+          <t>75777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>97310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136584</t>
+          <t>138943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380221</t>
+          <t>378714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432308</t>
+          <t>431778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389841</t>
+          <t>389538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440713</t>
+          <t>444136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784115</t>
+          <t>782635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859548</t>
+          <t>858837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125797</t>
+          <t>127835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173463</t>
+          <t>174703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59593</t>
+          <t>59820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93456</t>
+          <t>94767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197379</t>
+          <t>196411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257481</t>
+          <t>256439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127664</t>
+          <t>125131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176345</t>
+          <t>173526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220114</t>
+          <t>218845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275437</t>
+          <t>276976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>359255</t>
+          <t>358221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>434152</t>
+          <t>429921</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87547</t>
+          <t>87396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126774</t>
+          <t>126547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>70738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>109261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169082</t>
+          <t>170304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223857</t>
+          <t>223469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558641</t>
+          <t>558036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625576</t>
+          <t>622990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>583840</t>
+          <t>582559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647368</t>
+          <t>647221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1157756</t>
+          <t>1163632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1251570</t>
+          <t>1261318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133220</t>
+          <t>133680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>181102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90615</t>
+          <t>90812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201074</t>
+          <t>201189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259583</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73087</t>
+          <t>75156</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>112459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144344</t>
+          <t>141111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190720</t>
+          <t>189566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>229328</t>
+          <t>230119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>287338</t>
+          <t>289617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77334</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119081</t>
+          <t>117744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72834</t>
+          <t>73188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110915</t>
+          <t>111880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159729</t>
+          <t>162818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>216240</t>
+          <t>218449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>376019</t>
+          <t>376098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>436217</t>
+          <t>436685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>407635</t>
+          <t>410083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>467561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>800542</t>
+          <t>802360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>884515</t>
+          <t>880351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49778</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152804</t>
+          <t>150606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200794</t>
+          <t>199912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60382</t>
+          <t>61147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95696</t>
+          <t>96041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221370</t>
+          <t>223519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283719</t>
+          <t>282788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135299</t>
+          <t>136559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>184205</t>
+          <t>188472</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>233835</t>
+          <t>236364</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289019</t>
+          <t>293377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>383225</t>
+          <t>382823</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>461317</t>
+          <t>458271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>69038</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107413</t>
+          <t>104826</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73666</t>
+          <t>71866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110422</t>
+          <t>108006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154152</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205217</t>
+          <t>202548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>475026</t>
+          <t>473951</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>538066</t>
+          <t>539637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>574271</t>
+          <t>574335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>638117</t>
+          <t>640026</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1067642</t>
+          <t>1074429</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1163129</t>
+          <t>1167202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68433</t>
+          <t>68233</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63953</t>
+          <t>63434</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104307</t>
+          <t>103137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>551820</t>
+          <t>552188</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>642291</t>
+          <t>639488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>240871</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>302236</t>
+          <t>307010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>816962</t>
+          <t>814080</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>930253</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>477526</t>
+          <t>480834</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561977</t>
+          <t>568499</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>791840</t>
+          <t>790360</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>895371</t>
+          <t>896698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1297649</t>
+          <t>1295407</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1443981</t>
+          <t>1434699</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>311467</t>
+          <t>314974</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>385516</t>
+          <t>386916</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>296776</t>
+          <t>299242</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>370602</t>
+          <t>368355</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>622930</t>
+          <t>621571</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>723286</t>
+          <t>726589</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1850558</t>
+          <t>1849050</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1975531</t>
+          <t>1972155</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2018523</t>
+          <t>2017947</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2138063</t>
+          <t>2135578</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3905641</t>
+          <t>3903159</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4073875</t>
+          <t>4073455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>41642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87204</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126526</t>
+          <t>127543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>40966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>71222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136616</t>
+          <t>138137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186357</t>
+          <t>186113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83028</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100903</t>
+          <t>101068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>125364</t>
+          <t>126542</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171665</t>
+          <t>174097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>32355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>27182</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51206</t>
+          <t>49404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75218</t>
+          <t>76606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439493</t>
+          <t>440552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488100</t>
+          <t>488854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456761</t>
+          <t>454670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501613</t>
+          <t>500854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911802</t>
+          <t>911960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977751</t>
+          <t>978328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37326</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138318</t>
+          <t>138457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188459</t>
+          <t>186643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59545</t>
+          <t>59326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91380</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209770</t>
+          <t>207255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>267245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84842</t>
+          <t>86506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123646</t>
+          <t>126484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142807</t>
+          <t>141896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190109</t>
+          <t>189900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>239267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>305044</t>
+          <t>300717</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82058</t>
+          <t>81178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61673</t>
+          <t>61514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97861</t>
+          <t>96782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118357</t>
+          <t>120097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165983</t>
+          <t>167534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>642366</t>
+          <t>642677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>704586</t>
+          <t>706372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681233</t>
+          <t>683108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>741712</t>
+          <t>745036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1338669</t>
+          <t>1344957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1435007</t>
+          <t>1433478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121391</t>
+          <t>121338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168574</t>
+          <t>166021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63447</t>
+          <t>61442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99159</t>
+          <t>97495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192551</t>
+          <t>193085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250939</t>
+          <t>249628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>94809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135592</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109137</t>
+          <t>110555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151361</t>
+          <t>152512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>215398</t>
+          <t>216650</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>272946</t>
+          <t>276628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>93032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67475</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102906</t>
+          <t>101129</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135788</t>
+          <t>134308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185032</t>
+          <t>185741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>390504</t>
+          <t>388932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>446103</t>
+          <t>443466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>459182</t>
+          <t>458434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>515537</t>
+          <t>512899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>865334</t>
+          <t>864877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945223</t>
+          <t>947301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160385</t>
+          <t>160669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>209278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>107004</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148321</t>
+          <t>149968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,47 +10226,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>310812</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>282088</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>347584</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>14,28%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>310812</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>278868</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>345660</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>14,12%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83219</t>
+          <t>84986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122380</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127090</t>
+          <t>125477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174036</t>
+          <t>176149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>219829</t>
+          <t>219291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>284516</t>
+          <t>283197</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54315</t>
+          <t>53938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85945</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,82 +10417,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>85313</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>68840</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>104982</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>154071</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>132661</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>181243</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>9,18%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>85313</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>68984</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>103288</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>154071</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>132007</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>180033</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>541664</t>
+          <t>541887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>601962</t>
+          <t>602952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>634817</t>
+          <t>637344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699111</t>
+          <t>702345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1193588</t>
+          <t>1192948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1283535</t>
+          <t>1281514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33374</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61216</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28484</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>52478</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>68007</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104964</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>551885</t>
+          <t>551539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>642525</t>
+          <t>638090</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>301051</t>
+          <t>300086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>370292</t>
+          <t>367898</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>869861</t>
+          <t>873370</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>986752</t>
+          <t>988886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>347590</t>
+          <t>347592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>423832</t>
+          <t>421293</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>484213</t>
+          <t>485595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>568485</t>
+          <t>577315</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>859747</t>
+          <t>857731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>969990</t>
+          <t>971126</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>200656</t>
+          <t>201667</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>258821</t>
+          <t>260338</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>251288</t>
+          <t>251511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>317523</t>
+          <t>315392</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>473122</t>
+          <t>471114</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>561843</t>
+          <t>560916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2073341</t>
+          <t>2078209</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2187139</t>
+          <t>2185951</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2294905</t>
+          <t>2293981</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2405724</t>
+          <t>2400929</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4393815</t>
+          <t>4392356</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4554412</t>
+          <t>4555345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>159141</t>
+          <t>177161</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136599</t>
+          <t>152373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188310</t>
+          <t>205620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>113917</t>
+          <t>126036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97470</t>
+          <t>108329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129023</t>
+          <t>142010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>273058</t>
+          <t>303198</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245874</t>
+          <t>273867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>307809</t>
+          <t>338259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50722</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69687</t>
+          <t>76404</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58151</t>
+          <t>61874</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>93683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>103277</t>
+          <t>115048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85671</t>
+          <t>94385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127112</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -11993,22 +11993,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22192</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40650</t>
+          <t>44623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49107</t>
+          <t>55100</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415169</t>
+          <t>444278</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385517</t>
+          <t>412311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439446</t>
+          <t>472822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460994</t>
+          <t>495319</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441167</t>
+          <t>474381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480764</t>
+          <t>519868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>876163</t>
+          <t>939598</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837531</t>
+          <t>903794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>907847</t>
+          <t>976784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634109</t>
+          <t>689408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634109</t>
+          <t>689408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634109</t>
+          <t>689408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>675405</t>
+          <t>732752</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675405</t>
+          <t>732752</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>675405</t>
+          <t>732752</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1309514</t>
+          <t>1422161</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1309514</t>
+          <t>1422161</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1309514</t>
+          <t>1422161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,17 +12371,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>203737</t>
+          <t>244447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93703</t>
+          <t>216713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271129</t>
+          <t>279851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152678</t>
+          <t>175375</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131611</t>
+          <t>152164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>174562</t>
+          <t>200547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>356415</t>
+          <t>419822</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241836</t>
+          <t>381800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>417142</t>
+          <t>459955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92808</t>
+          <t>113500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41382</t>
+          <t>88991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126371</t>
+          <t>143281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136685</t>
+          <t>156099</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116361</t>
+          <t>135699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156569</t>
+          <t>180598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>229493</t>
+          <t>269599</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155989</t>
+          <t>237093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271050</t>
+          <t>305275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>288055</t>
+          <t>46676</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>32511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>742369</t>
+          <t>64938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46148</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71357</t>
+          <t>75817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>345070</t>
+          <t>107463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105549</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>909914</t>
+          <t>130350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>589481</t>
+          <t>630836</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289893</t>
+          <t>588531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>756855</t>
+          <t>663711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>607051</t>
+          <t>672725</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>578448</t>
+          <t>643569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633382</t>
+          <t>701390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1196532</t>
+          <t>1303561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>816546</t>
+          <t>1255905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1368342</t>
+          <t>1349720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1181812</t>
+          <t>1045292</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1181812</t>
+          <t>1045292</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1181812</t>
+          <t>1045292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956077</t>
+          <t>1067991</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956077</t>
+          <t>1067991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956077</t>
+          <t>1067991</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2137889</t>
+          <t>2113283</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2137889</t>
+          <t>2113283</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2137889</t>
+          <t>2113283</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>33808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>192952</t>
+          <t>226006</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166683</t>
+          <t>196624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>224630</t>
+          <t>257918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80593</t>
+          <t>99942</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>82959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112439</t>
+          <t>122166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>273546</t>
+          <t>325948</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180449</t>
+          <t>286549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326581</t>
+          <t>364012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>82048</t>
+          <t>94927</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64519</t>
+          <t>75703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104401</t>
+          <t>120536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>114311</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>119672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157122</t>
+          <t>161577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>196359</t>
+          <t>234961</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126508</t>
+          <t>204592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>238692</t>
+          <t>264535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>83275</t>
+          <t>94414</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>79372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113615</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>142565</t>
+          <t>163215</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95547</t>
+          <t>138601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176562</t>
+          <t>188120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>353637</t>
+          <t>396247</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322615</t>
+          <t>364705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>383200</t>
+          <t>429052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>650065</t>
+          <t>472613</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>555753</t>
+          <t>444875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>795718</t>
+          <t>499303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1003702</t>
+          <t>868859</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899292</t>
+          <t>827550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1219436</t>
+          <t>917189</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>702581</t>
+          <t>800873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>702581</t>
+          <t>800873</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>702581</t>
+          <t>800873</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930972</t>
+          <t>809829</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930972</t>
+          <t>809829</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930972</t>
+          <t>809829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1633553</t>
+          <t>1610702</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1633553</t>
+          <t>1610702</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1633553</t>
+          <t>1610702</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>14718</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>24667</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>233781</t>
+          <t>254674</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201936</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263829</t>
+          <t>285101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127401</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185050</t>
+          <t>207366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>395073</t>
+          <t>436186</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>349445</t>
+          <t>399631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>442761</t>
+          <t>482888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -13926,27 +13926,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73740</t>
+          <t>80303</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>63668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91483</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>99333</t>
+          <t>109948</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79580</t>
+          <t>93686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119331</t>
+          <t>129156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>173073</t>
+          <t>190250</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>167661</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199627</t>
+          <t>213915</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>56716</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71647</t>
+          <t>74917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>70945</t>
+          <t>77858</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>92268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>125866</t>
+          <t>134574</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101825</t>
+          <t>114323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>146679</t>
+          <t>157302</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>554569</t>
+          <t>585272</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>523991</t>
+          <t>550708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>589255</t>
+          <t>618028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>752964</t>
+          <t>739043</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718912</t>
+          <t>707920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824461</t>
+          <t>768120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1307533</t>
+          <t>1324315</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1259087</t>
+          <t>1275162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1386615</t>
+          <t>1367932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>922271</t>
+          <t>985555</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>922271</t>
+          <t>985555</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>922271</t>
+          <t>985555</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1088963</t>
+          <t>1114488</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1088963</t>
+          <t>1114488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1088963</t>
+          <t>1114488</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2011234</t>
+          <t>2100043</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2011234</t>
+          <t>2100043</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2011234</t>
+          <t>2100043</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,102 +14382,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53581</t>
+          <t>61483</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>13226</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>8241</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>20448</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>54491</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>39925</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>72687</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>10984</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6733</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>17095</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>45361</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>30800</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>66764</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>789611</t>
+          <t>902288</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>612285</t>
+          <t>844333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>871588</t>
+          <t>965530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>508480</t>
+          <t>582866</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>417820</t>
+          <t>544384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>560606</t>
+          <t>627541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1298091</t>
+          <t>1485154</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1119069</t>
+          <t>1413007</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402991</t>
+          <t>1564930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>282186</t>
+          <t>327374</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>221838</t>
+          <t>286136</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>324660</t>
+          <t>370237</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>420015</t>
+          <t>482485</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>446661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>465546</t>
+          <t>519620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>702201</t>
+          <t>809858</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>612226</t>
+          <t>757087</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>767923</t>
+          <t>869329</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>421745</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>182904</t>
+          <t>162912</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1047063</t>
+          <t>226637</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>240864</t>
+          <t>266782</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>196410</t>
+          <t>241896</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>271580</t>
+          <t>295801</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>662608</t>
+          <t>460353</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>423660</t>
+          <t>418134</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1442278</t>
+          <t>503633</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1912855</t>
+          <t>2056632</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1510435</t>
+          <t>1988517</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2080029</t>
+          <t>2125330</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2471073</t>
+          <t>2379700</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2371139</t>
+          <t>2330001</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2688514</t>
+          <t>2432939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4383929</t>
+          <t>4436332</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3856563</t>
+          <t>4355962</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4610202</t>
+          <t>4523420</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3440773</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3440773</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3440773</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3651417</t>
+          <t>3725060</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3651417</t>
+          <t>3725060</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3651417</t>
+          <t>3725060</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7092190</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7092190</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7092190</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
